--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104663_W23.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104663_W23.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3729</v>
+        <v>5.7974</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9057</v>
+        <v>3.8544</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4671</v>
+        <v>1.9429</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1291</v>
+        <v>3.1123</v>
       </c>
       <c r="H2" t="n">
-        <v>2.2628</v>
+        <v>2.2468</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8663</v>
+        <v>0.8653999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7325</v>
+        <v>3.6852</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4767</v>
+        <v>3.4399</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2558</v>
+        <v>0.2453</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6034</v>
+        <v>-0.5729</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.2139</v>
+        <v>-1.1931</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6105</v>
+        <v>0.6201</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4367</v>
+        <v>0.0022</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2148</v>
+        <v>0.2179</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6515</v>
+        <v>-0.2157</v>
       </c>
       <c r="V2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>M. SPAGNOLO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3916</v>
+        <v>3.5989</v>
       </c>
       <c r="E3" t="n">
-        <v>1.572</v>
+        <v>0.6905</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8196</v>
+        <v>2.9084</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.6859</v>
+        <v>0.6001</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4647</v>
+        <v>0.7952</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2212</v>
+        <v>-0.1952</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.002</v>
+        <v>0.324</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.4471</v>
+        <v>0.8683</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4451</v>
+        <v>-0.5443</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6839</v>
+        <v>0.276</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0176</v>
+        <v>-0.0731</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6663</v>
+        <v>0.3492</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2683</v>
+        <v>2.0487</v>
       </c>
       <c r="S3" t="n">
-        <v>2.9168</v>
+        <v>0.8411</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6816</v>
+        <v>0.2574</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2352</v>
+        <v>0.5837</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. SPAGNOLO</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2072</v>
+        <v>3.1652</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.09669999999999999</v>
+        <v>2.7002</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3038</v>
+        <v>0.4649</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5946</v>
+        <v>3.8874</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7892</v>
+        <v>4.7797</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1946</v>
+        <v>-0.8924</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3557</v>
+        <v>4.4274</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8863</v>
+        <v>4.4504</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5306</v>
+        <v>-0.023</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2389</v>
+        <v>-0.54</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.09710000000000001</v>
+        <v>0.3294</v>
       </c>
       <c r="O4" t="n">
-        <v>0.336</v>
+        <v>-0.8694</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9073</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>-3.6421</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0415</v>
+        <v>1.8211</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4518</v>
+        <v>0.5541</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5716</v>
+        <v>0.2808</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0234</v>
+        <v>0.2733</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2534</v>
+        <v>0.5447</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2534</v>
+        <v>1.6342</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>R. VILLAR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7226</v>
+        <v>3.1531</v>
       </c>
       <c r="E5" t="n">
-        <v>2.6398</v>
+        <v>2.062</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0828</v>
+        <v>1.0911</v>
       </c>
       <c r="G5" t="n">
-        <v>3.9005</v>
+        <v>-0.0156</v>
       </c>
       <c r="H5" t="n">
-        <v>4.7908</v>
+        <v>0.5455</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8903</v>
+        <v>-0.5612</v>
       </c>
       <c r="J5" t="n">
-        <v>4.4698</v>
+        <v>1.5024</v>
       </c>
       <c r="K5" t="n">
-        <v>4.4779</v>
+        <v>1.4651</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0081</v>
+        <v>0.0372</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5693</v>
+        <v>-1.518</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3129</v>
+        <v>-0.9196</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8822</v>
+        <v>-0.5984</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.6293</v>
+        <v>-0.2276</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8147</v>
+        <v>2.0487</v>
       </c>
       <c r="S5" t="n">
-        <v>0.09039999999999999</v>
+        <v>-0.5157</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1603</v>
+        <v>-0.3022</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0699</v>
+        <v>-0.2135</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5463</v>
+        <v>1.8634</v>
       </c>
       <c r="W5" t="n">
-        <v>1.639</v>
+        <v>1.0895</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0927</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. VILLAR</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.6502</v>
+        <v>2.9038</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8367</v>
+        <v>0.4861</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8135</v>
+        <v>2.4177</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0278</v>
+        <v>-0.6756</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5425</v>
+        <v>-0.4598</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5703</v>
+        <v>-0.2158</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5092</v>
+        <v>-0.0197</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4719</v>
+        <v>-0.4589</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0373</v>
+        <v>0.4392</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5371</v>
+        <v>-0.6558</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9294</v>
+        <v>-0.0009</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6077</v>
+        <v>-0.6549</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8147</v>
+        <v>0.9105</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0415</v>
+        <v>2.2763</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0005</v>
+        <v>1.4216</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5383</v>
+        <v>0.6244</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4621</v>
+        <v>0.7972</v>
       </c>
       <c r="V6" t="n">
-        <v>1.8639</v>
+        <v>1.2472</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0927</v>
+        <v>1.2472</v>
       </c>
       <c r="X6" t="n">
-        <v>0.7712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7747000000000001</v>
+        <v>1.17</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3607</v>
+        <v>0.5663</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4139</v>
+        <v>0.6037</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.1259</v>
+        <v>-2.1205</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3765</v>
+        <v>1.3785</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.5025</v>
+        <v>-3.499</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8689</v>
+        <v>-0.8923</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3782</v>
+        <v>1.365</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.2471</v>
+        <v>-2.2572</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.257</v>
+        <v>-1.2282</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0017</v>
+        <v>0.0135</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.2554</v>
+        <v>-1.2417</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R7" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7153</v>
+        <v>1.1115</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4053</v>
+        <v>0.6454</v>
       </c>
       <c r="U7" t="n">
-        <v>0.31</v>
+        <v>0.4661</v>
       </c>
       <c r="V7" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W7" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5259</v>
+        <v>0.5577</v>
       </c>
       <c r="E8" t="n">
-        <v>1.0404</v>
+        <v>1.037</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5145</v>
+        <v>-0.4793</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7449</v>
+        <v>-0.7419</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1559</v>
+        <v>-0.1551</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7622</v>
+        <v>-0.7592</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0487</v>
+        <v>-0.0174</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0696</v>
+        <v>-0.0697</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0209</v>
+        <v>0.0523</v>
       </c>
       <c r="V8" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3233</v>
+        <v>-0.4446</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0522</v>
+        <v>-0.0525</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2711</v>
+        <v>-0.3921</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7449</v>
+        <v>-0.7419</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1559</v>
+        <v>-0.1551</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7622</v>
+        <v>-0.7592</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1948</v>
+        <v>0.0697</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0696</v>
+        <v>-0.0697</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2643</v>
+        <v>0.1394</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9307</v>
+        <v>-1.2491</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3551</v>
+        <v>-2.6445</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4244</v>
+        <v>1.3954</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4917</v>
+        <v>0.4781</v>
       </c>
       <c r="H10" t="n">
-        <v>2.0377</v>
+        <v>2.0228</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.546</v>
+        <v>-1.5447</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6206</v>
+        <v>1.5801</v>
       </c>
       <c r="K10" t="n">
-        <v>3.3452</v>
+        <v>3.316</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.7247</v>
+        <v>-1.7359</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1289</v>
+        <v>-1.102</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3075</v>
+        <v>-1.2932</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1787</v>
+        <v>0.1912</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3242</v>
+        <v>0.0256</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0393</v>
+        <v>-0.1955</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2849</v>
+        <v>0.2211</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9027</v>
+        <v>-1.8054</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0905</v>
+        <v>0.0101</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8122</v>
+        <v>-1.8155</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.4234</v>
+        <v>-1.4254</v>
       </c>
       <c r="H11" t="n">
-        <v>1.6073</v>
+        <v>1.6138</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.0308</v>
+        <v>-3.0392</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7045</v>
+        <v>-0.7259</v>
       </c>
       <c r="K11" t="n">
-        <v>1.2468</v>
+        <v>1.2411</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.9513</v>
+        <v>-1.967</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7189</v>
+        <v>-0.6995</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3605</v>
+        <v>0.3727</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0795</v>
+        <v>-1.0722</v>
       </c>
       <c r="P11" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5719</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>0.614</v>
+        <v>0.736</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0421</v>
+        <v>-0.0752</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.9383</v>
+        <v>-2.2904</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5112</v>
+        <v>-0.7615</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4271</v>
+        <v>-1.529</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0322</v>
+        <v>0.0388</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1198</v>
+        <v>-0.1179</v>
       </c>
       <c r="I12" t="n">
-        <v>0.152</v>
+        <v>0.1566</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7802</v>
+        <v>0.77</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6682</v>
+        <v>0.6583</v>
       </c>
       <c r="L12" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.748</v>
+        <v>-0.7312</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.788</v>
+        <v>-0.7761</v>
       </c>
       <c r="O12" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6666</v>
+        <v>0.3066</v>
       </c>
       <c r="T12" t="n">
-        <v>0.614</v>
+        <v>0.3807</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0526</v>
+        <v>-0.0741</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.4102</v>
+        <v>-2.4082</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>14.5501</v>
+        <v>14.5566</v>
       </c>
       <c r="E13" t="n">
-        <v>8.249600000000001</v>
+        <v>7.9481</v>
       </c>
       <c r="F13" t="n">
-        <v>6.3002</v>
+        <v>6.6082</v>
       </c>
       <c r="G13" t="n">
-        <v>2.395299999999999</v>
+        <v>2.395799999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>12.5105</v>
+        <v>12.4944</v>
       </c>
       <c r="I13" t="n">
-        <v>-10.1156</v>
+        <v>-10.0991</v>
       </c>
       <c r="J13" t="n">
-        <v>10.9272</v>
+        <v>10.6856</v>
       </c>
       <c r="K13" t="n">
-        <v>16.5387</v>
+        <v>16.3796</v>
       </c>
       <c r="L13" t="n">
-        <v>-5.6116</v>
+        <v>-5.694</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.532</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.0282</v>
+        <v>-3.8852</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.5041</v>
+        <v>-4.4048</v>
       </c>
       <c r="P13" t="n">
-        <v>3.4024</v>
+        <v>3.414400000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>-13.61</v>
+        <v>-13.658</v>
       </c>
       <c r="R13" t="n">
-        <v>17.0124</v>
+        <v>17.0724</v>
       </c>
       <c r="S13" t="n">
-        <v>4.445899999999999</v>
+        <v>4.460099999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>2.4802</v>
+        <v>2.5055</v>
       </c>
       <c r="U13" t="n">
-        <v>1.9657</v>
+        <v>1.9546</v>
       </c>
       <c r="V13" t="n">
-        <v>4.3066</v>
+        <v>4.2863</v>
       </c>
       <c r="W13" t="n">
-        <v>8.452399999999999</v>
+        <v>8.415100000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.145799999999999</v>
+        <v>-4.1287</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.7426</v>
+        <v>5.6286</v>
       </c>
       <c r="E14" t="n">
-        <v>6.5598</v>
+        <v>6.4084</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8171</v>
+        <v>-0.7798</v>
       </c>
       <c r="G14" t="n">
-        <v>3.9148</v>
+        <v>3.9084</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5714</v>
+        <v>2.5678</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3434</v>
+        <v>1.3405</v>
       </c>
       <c r="J14" t="n">
-        <v>4.4228</v>
+        <v>4.3947</v>
       </c>
       <c r="K14" t="n">
-        <v>3.5326</v>
+        <v>3.5163</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8902</v>
+        <v>0.8783</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.508</v>
+        <v>-0.4863</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9485</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4532</v>
+        <v>0.4622</v>
       </c>
       <c r="P14" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0529</v>
+        <v>-0.1707</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0484</v>
+        <v>-0.1652</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0046</v>
+        <v>-0.0055</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W14" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="15">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2542</v>
+        <v>0.2875</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0224</v>
+        <v>0.022</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2318</v>
+        <v>0.2655</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0761</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1559</v>
+        <v>-0.1551</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2319</v>
+        <v>0.2324</v>
       </c>
       <c r="J15" t="n">
-        <v>0.092</v>
+        <v>0.0917</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0159</v>
+        <v>-0.0144</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0487</v>
+        <v>-0.0174</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0696</v>
+        <v>-0.0697</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0209</v>
+        <v>0.0523</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0832</v>
+        <v>0.0898</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9285</v>
+        <v>-1.3132</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0117</v>
+        <v>1.403</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9291</v>
+        <v>0.9156</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.886</v>
+        <v>-0.8847</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8151</v>
+        <v>1.8003</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0404</v>
+        <v>1.0167</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1456</v>
+        <v>-0.1519</v>
       </c>
       <c r="L16" t="n">
-        <v>1.186</v>
+        <v>1.1686</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1113</v>
+        <v>-0.1011</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.7328</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6291</v>
+        <v>0.6317</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2882</v>
+        <v>0.3123</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2994</v>
+        <v>-0.0536</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0112</v>
+        <v>0.3659</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3833</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0457</v>
+        <v>1.1323</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.4291</v>
+        <v>-1.0516</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5081</v>
+        <v>1.5059</v>
       </c>
       <c r="H17" t="n">
-        <v>0.863</v>
+        <v>0.8562</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6451</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>2.4369</v>
+        <v>2.4079</v>
       </c>
       <c r="K17" t="n">
-        <v>2.0292</v>
+        <v>2.006</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4078</v>
+        <v>0.4019</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9288999999999999</v>
+        <v>-0.902</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1662</v>
+        <v>-1.1497</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2373</v>
+        <v>0.2477</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7988</v>
+        <v>-0.3357</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2571</v>
+        <v>-0.1375</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5417</v>
+        <v>-0.1983</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9035</v>
+        <v>-0.4901</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1196</v>
+        <v>0.2119</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7838000000000001</v>
+        <v>-0.702</v>
       </c>
       <c r="G18" t="n">
-        <v>1.9803</v>
+        <v>1.9791</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8528</v>
+        <v>0.853</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1275</v>
+        <v>1.1261</v>
       </c>
       <c r="J18" t="n">
-        <v>2.4965</v>
+        <v>2.4814</v>
       </c>
       <c r="K18" t="n">
-        <v>1.9395</v>
+        <v>1.9305</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5162</v>
+        <v>-0.5023</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0867</v>
+        <v>-1.0775</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5705</v>
+        <v>0.5752</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4301</v>
+        <v>-0.0139</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3478</v>
+        <v>0.0068</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0823</v>
+        <v>-0.0207</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. BRUNOT</t>
+          <t>P. VILDOZA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9475</v>
+        <v>-0.7154</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4944</v>
+        <v>0.081</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4531</v>
+        <v>-0.7963</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.0269</v>
+        <v>-1.3901</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0188</v>
+        <v>-1.6431</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.008</v>
+        <v>0.253</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5851</v>
+        <v>0.332</v>
       </c>
       <c r="K19" t="n">
-        <v>0.052</v>
+        <v>0.1239</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6371</v>
+        <v>0.2081</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4417</v>
+        <v>-1.7221</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.0708</v>
+        <v>-1.767</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6291</v>
+        <v>0.0449</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0378</v>
+        <v>-0.4634</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0907</v>
+        <v>-0.251</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0529</v>
+        <v>-0.2124</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. VILDOZA</t>
+          <t>K. BRUNOT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2669</v>
+        <v>-1.0915</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.137</v>
+        <v>-0.9702</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1299</v>
+        <v>-0.1213</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.3894</v>
+        <v>-1.0204</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.6479</v>
+        <v>-1.0114</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2585</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3499</v>
+        <v>-0.589</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1314</v>
+        <v>0.0517</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2185</v>
+        <v>-0.6407</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7393</v>
+        <v>-0.4314</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.7794</v>
+        <v>-1.0631</v>
       </c>
       <c r="O20" t="n">
-        <v>0.04</v>
+        <v>0.6317</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0117</v>
+        <v>-0.1198</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4869</v>
+        <v>-0.3812</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5247000000000001</v>
+        <v>0.2614</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0097</v>
+        <v>-1.5203</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5439000000000001</v>
+        <v>-0.4389</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4658</v>
+        <v>-1.0814</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.9509</v>
+        <v>-1.9246</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.2628</v>
+        <v>-2.2468</v>
       </c>
       <c r="I21" t="n">
-        <v>0.312</v>
+        <v>0.3222</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0329</v>
+        <v>0.026</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.0417</v>
+        <v>-0.0485</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.9838</v>
+        <v>-1.9506</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.2211</v>
+        <v>-2.1984</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2373</v>
+        <v>0.2477</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9908</v>
+        <v>-0.5274</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5353</v>
+        <v>-0.4163</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4555</v>
+        <v>-0.1111</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4663</v>
+        <v>-2.1076</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5391</v>
+        <v>-2.3438</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0728</v>
+        <v>0.2362</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3048</v>
+        <v>-0.3096</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.8743</v>
+        <v>-2.8776</v>
       </c>
       <c r="I22" t="n">
-        <v>2.5696</v>
+        <v>2.568</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1255</v>
+        <v>0.091</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.3618</v>
+        <v>-1.3832</v>
       </c>
       <c r="L22" t="n">
-        <v>1.4873</v>
+        <v>1.4741</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4302</v>
+        <v>-0.4006</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.5125</v>
+        <v>-1.4945</v>
       </c>
       <c r="O22" t="n">
-        <v>1.0823</v>
+        <v>1.0939</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3883</v>
+        <v>-0.0256</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3962</v>
+        <v>-0.1584</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0078</v>
+        <v>0.1328</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1834</v>
+        <v>-2.5436</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.09</v>
+        <v>-2.7581</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0934</v>
+        <v>0.2145</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.3776</v>
+        <v>-2.374</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.4358</v>
+        <v>-3.4269</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0582</v>
+        <v>1.0529</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.1211</v>
+        <v>-1.1388</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.4515</v>
+        <v>-1.4586</v>
       </c>
       <c r="L23" t="n">
-        <v>0.3304</v>
+        <v>0.3198</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.2566</v>
+        <v>-1.2351</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.9843</v>
+        <v>-1.9683</v>
       </c>
       <c r="O23" t="n">
-        <v>0.7277</v>
+        <v>0.7331</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0325</v>
+        <v>-0.3973</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8347</v>
+        <v>-0.4811</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1978</v>
+        <v>0.0838</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>N. MARIC</t>
+          <t>O. LIVINGSTON</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.6575</v>
+        <v>-3.7511</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.5711</v>
+        <v>-1.7386</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0864</v>
+        <v>-2.0125</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.2603</v>
+        <v>-1.4992</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.6895</v>
+        <v>-1.8267</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4292</v>
+        <v>0.3275</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.3391</v>
+        <v>0.5369</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.4138</v>
+        <v>0.7165</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0746</v>
+        <v>-0.1796</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.9212</v>
+        <v>-2.036</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.2758</v>
+        <v>-2.5431</v>
       </c>
       <c r="O24" t="n">
-        <v>0.3546</v>
+        <v>0.5071</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.1757</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2268</v>
+        <v>1.5934</v>
       </c>
       <c r="S24" t="n">
-        <v>2.0318</v>
+        <v>-0.9756</v>
       </c>
       <c r="T24" t="n">
-        <v>1.9417</v>
+        <v>-0.4952</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0901</v>
+        <v>-0.4804</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.2534</v>
+        <v>0.5447</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.7712</v>
+        <v>1.6342</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.4822</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>O. LIVINGSTON</t>
+          <t>N. MARIC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.8119</v>
+        <v>-6.0547</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.5046</v>
+        <v>-4.901</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.3073</v>
+        <v>-1.1536</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.4936</v>
+        <v>-2.264</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.8268</v>
+        <v>-2.6992</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3331</v>
+        <v>0.4352</v>
       </c>
       <c r="J25" t="n">
-        <v>0.5805</v>
+        <v>-1.3604</v>
       </c>
       <c r="K25" t="n">
-        <v>0.7406</v>
+        <v>-1.4349</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.1601</v>
+        <v>0.0745</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.0742</v>
+        <v>-0.9036</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.5674</v>
+        <v>-1.2643</v>
       </c>
       <c r="O25" t="n">
-        <v>0.4932</v>
+        <v>0.3608</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.8147</v>
+        <v>-3.1868</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5878</v>
+        <v>0.2276</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.05</v>
+        <v>0.6434</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.3217</v>
+        <v>0.6478</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.7282999999999999</v>
+        <v>-0.0044</v>
       </c>
       <c r="V25" t="n">
-        <v>0.5463</v>
+        <v>-1.2472</v>
       </c>
       <c r="W25" t="n">
-        <v>1.639</v>
+        <v>-0.7739</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.0927</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-14.55</v>
+        <v>-12.1877</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.300299999999999</v>
+        <v>-6.608199999999998</v>
       </c>
       <c r="F26" t="n">
-        <v>-8.249600000000001</v>
+        <v>-5.579299999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.3951</v>
+        <v>-2.3956</v>
       </c>
       <c r="H26" t="n">
-        <v>-12.5106</v>
+        <v>-12.4945</v>
       </c>
       <c r="I26" t="n">
-        <v>10.1156</v>
+        <v>10.0988</v>
       </c>
       <c r="J26" t="n">
-        <v>8.5321</v>
+        <v>8.290099999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>4.0282</v>
+        <v>3.885</v>
       </c>
       <c r="L26" t="n">
-        <v>4.5038</v>
+        <v>4.4049</v>
       </c>
       <c r="M26" t="n">
-        <v>-10.9273</v>
+        <v>-10.6855</v>
       </c>
       <c r="N26" t="n">
-        <v>-16.539</v>
+        <v>-16.3796</v>
       </c>
       <c r="O26" t="n">
-        <v>5.611599999999999</v>
+        <v>5.693900000000001</v>
       </c>
       <c r="P26" t="n">
-        <v>-3.4026</v>
+        <v>-3.414499999999999</v>
       </c>
       <c r="Q26" t="n">
-        <v>-17.0125</v>
+        <v>-17.0725</v>
       </c>
       <c r="R26" t="n">
-        <v>13.61</v>
+        <v>13.658</v>
       </c>
       <c r="S26" t="n">
-        <v>-4.446</v>
+        <v>-2.0911</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.9659</v>
+        <v>-1.9546</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.4802</v>
+        <v>-0.1366</v>
       </c>
       <c r="V26" t="n">
-        <v>-4.3066</v>
+        <v>-4.2866</v>
       </c>
       <c r="W26" t="n">
-        <v>4.145799999999999</v>
+        <v>4.128699999999999</v>
       </c>
       <c r="X26" t="n">
-        <v>-8.452499999999999</v>
+        <v>-8.4153</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104663_W23.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104663_W23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104663_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104663_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104663_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104663_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104663_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104663_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104663_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104663_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104663_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104663_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104663_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-4.1287</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104663_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104663_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104663_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104663_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104663_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104663_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104663_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104663_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104663_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104663_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104663_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104663_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-8.4153</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
